--- a/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -524,7 +524,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -545,7 +545,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
+          <t>61T7bt5t</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -587,7 +587,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>2m3cvwKO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -608,7 +608,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
+          <t>fNaktakC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -650,7 +650,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
+          <t>dCkAk3SP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -671,7 +671,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
+          <t>U5cORazJ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -797,7 +797,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
+          <t>tIUiyD7F</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -839,7 +839,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>tIUiyD7F</t>
+          <t>hdlcFVpd</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>

--- a/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>GdWtpsjm</t>
+          <t>z1q67ylB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -524,7 +524,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -545,7 +545,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -566,7 +566,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
+          <t>INsZAAf3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -587,7 +587,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -608,7 +608,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
+          <t>8QPOfb45</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -629,7 +629,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
+          <t>lpob9cJb</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -650,7 +650,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
+          <t>x6HuiG3U</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -671,7 +671,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>2Fanm72d</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -692,7 +692,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
+          <t>ERWFdKZh</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -713,7 +713,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>AeRSxQrK</t>
+          <t>GdWtpsjm</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -734,7 +734,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>fmqtFMjD</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -755,7 +755,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>8WpYGrM0</t>
+          <t>61T7bt5t</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -776,7 +776,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>nHdPI4il</t>
+          <t>2g67Vsyf</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -797,7 +797,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>tIUiyD7F</t>
+          <t>lAUlrLKa</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -818,7 +818,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>pjyqwZx3</t>
+          <t>U5cORazJ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -839,7 +839,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
+          <t>dCkAk3SP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -860,7 +860,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>CntkHiGq</t>
+          <t>2m3cvwKO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -881,7 +881,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>t4kJMDhM</t>
+          <t>fNaktakC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -902,7 +902,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Kl1AOZN9</t>
+          <t>8j9FTL56</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -920,6 +920,27 @@
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>AeRSxQrK</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>GdWtpsjm</t>
+          <t>z1q67ylB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -524,7 +524,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -545,7 +545,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -566,7 +566,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
+          <t>INsZAAf3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -587,7 +587,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
+          <t>8QPOfb45</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -608,7 +608,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
+          <t>lpob9cJb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -629,7 +629,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
+          <t>x6HuiG3U</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -650,7 +650,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
+          <t>2Fanm72d</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -671,7 +671,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -692,7 +692,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
+          <t>ERWFdKZh</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -713,7 +713,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>AeRSxQrK</t>
+          <t>GdWtpsjm</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -734,7 +734,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>fmqtFMjD</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -755,7 +755,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>8WpYGrM0</t>
+          <t>61T7bt5t</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -776,7 +776,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>nHdPI4il</t>
+          <t>2g67Vsyf</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -797,7 +797,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>tIUiyD7F</t>
+          <t>dCkAk3SP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -818,7 +818,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>pjyqwZx3</t>
+          <t>lAUlrLKa</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -839,7 +839,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
+          <t>fNaktakC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -860,7 +860,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>CntkHiGq</t>
+          <t>2m3cvwKO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -881,7 +881,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>t4kJMDhM</t>
+          <t>U5cORazJ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -902,7 +902,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Kl1AOZN9</t>
+          <t>8j9FTL56</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>

--- a/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -524,7 +524,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U11vkTXq</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -545,7 +545,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tvOWhxZH</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -587,7 +587,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>8QPOfb45</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -608,7 +608,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>lpob9cJb</t>
+          <t>x6HuiG3U</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -629,7 +629,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>x6HuiG3U</t>
+          <t>8QPOfb45</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -671,7 +671,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>SUdkBJln</t>
+          <t>lpob9cJb</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -734,7 +734,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
+          <t>61T7bt5t</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -755,7 +755,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -860,7 +860,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
+          <t>U5cORazJ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -881,7 +881,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>2m3cvwKO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>

--- a/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z1q67ylB</t>
+          <t>2g67Vsyf</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -524,7 +524,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>tvOWhxZH</t>
+          <t>U5cORazJ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -545,7 +545,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>U11vkTXq</t>
+          <t>2m3cvwKO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -566,7 +566,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>INsZAAf3</t>
+          <t>lAUlrLKa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -587,7 +587,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>SUdkBJln</t>
+          <t>fNaktakC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -608,7 +608,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>x6HuiG3U</t>
+          <t>dCkAk3SP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -629,7 +629,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8QPOfb45</t>
+          <t>8j9FTL56</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -647,279 +647,6 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>2Fanm72d</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>lpob9cJb</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>ERWFdKZh</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>GdWtpsjm</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>61T7bt5t</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>6RCbX36s</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>2g67Vsyf</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>dCkAk3SP</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>lAUlrLKa</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>fNaktakC</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>U5cORazJ</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>2m3cvwKO</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>8j9FTL56</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
+          <t>z1q67ylB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -524,7 +524,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -545,7 +545,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -566,7 +566,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
+          <t>INsZAAf3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -587,7 +587,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
+          <t>2Fanm72d</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -608,7 +608,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -629,7 +629,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
+          <t>lpob9cJb</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -647,6 +647,132 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>x6HuiG3U</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8QPOfb45</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ERWFdKZh</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>GdWtpsjm</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>6RCbX36s</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>61T7bt5t</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,7 +524,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>tvOWhxZH</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -545,7 +545,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>U11vkTXq</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -587,7 +587,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2Fanm72d</t>
+          <t>8QPOfb45</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -608,7 +608,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SUdkBJln</t>
+          <t>2Fanm72d</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -629,7 +629,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>lpob9cJb</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -650,7 +650,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>x6HuiG3U</t>
+          <t>lpob9cJb</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -671,7 +671,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>8QPOfb45</t>
+          <t>x6HuiG3U</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -710,69 +710,6 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>GdWtpsjm</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>6RCbX36s</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>61T7bt5t</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z1q67ylB</t>
+          <t>AVat9lPF</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -524,7 +524,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U11vkTXq</t>
+          <t>Wplk7SgS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -545,7 +545,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tvOWhxZH</t>
+          <t>tzSnG5Wr</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -566,7 +566,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>INsZAAf3</t>
+          <t>beYTapn2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -587,7 +587,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>8QPOfb45</t>
+          <t>2TvL16Hk</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -608,7 +608,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2Fanm72d</t>
+          <t>AiyHLR8L</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -629,7 +629,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>SUdkBJln</t>
+          <t>jkLFNmv9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -650,7 +650,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>lpob9cJb</t>
+          <t>2kGeEq1e</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -671,7 +671,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>x6HuiG3U</t>
+          <t>z1q67ylB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -692,7 +692,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ERWFdKZh</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -710,6 +710,174 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>U11vkTXq</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>INsZAAf3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>SUdkBJln</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>x6HuiG3U</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>2Fanm72d</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>lpob9cJb</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>8QPOfb45</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ERWFdKZh</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,60 +441,65 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>mean_last_match_mean_rat_player_start_away_against</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_hei_player_start</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_start</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_start</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_sub</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
@@ -503,7 +508,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AVat9lPF</t>
+          <t>z1q67ylB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -520,11 +525,12 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Wplk7SgS</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -541,11 +547,12 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tzSnG5Wr</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -562,321 +569,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>beYTapn2</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>2TvL16Hk</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>AiyHLR8L</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>jkLFNmv9</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>2kGeEq1e</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>z1q67ylB</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>tvOWhxZH</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>U11vkTXq</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>INsZAAf3</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>SUdkBJln</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>x6HuiG3U</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>2Fanm72d</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>lpob9cJb</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>8QPOfb45</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>ERWFdKZh</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z1q67ylB</t>
+          <t>Of1jzRNE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -530,7 +530,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>tvOWhxZH</t>
+          <t>AFJ3CNV7</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -552,7 +552,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>U11vkTXq</t>
+          <t>AVat9lPF</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -571,6 +571,160 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Wplk7SgS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2TvL16Hk</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>beYTapn2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>jkLFNmv9</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>AiyHLR8L</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>tzSnG5Wr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>2kGeEq1e</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,74 +441,64 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_away_against</t>
+          <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_hei_player_start</t>
+          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_int_rep_player_sub</t>
+          <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Of1jzRNE</t>
+          <t>UwFBuMaf</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -524,13 +514,11 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>AFJ3CNV7</t>
+          <t>GhtVSrGl</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -546,13 +534,11 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AVat9lPF</t>
+          <t>OIqwRMp1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -568,13 +554,11 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Wplk7SgS</t>
+          <t>pYXoP0FD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -590,13 +574,11 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2TvL16Hk</t>
+          <t>d8abY4hR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -612,13 +594,11 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>beYTapn2</t>
+          <t>W2BSyvaJ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -634,13 +614,11 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jkLFNmv9</t>
+          <t>Q58Kw0U6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -656,13 +634,11 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>AiyHLR8L</t>
+          <t>dQG3srVs</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -678,13 +654,11 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>tzSnG5Wr</t>
+          <t>xtzXn47K</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -700,13 +674,11 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2kGeEq1e</t>
+          <t>C0axT3Xo</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -722,8 +694,206 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Of1jzRNE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>AFJ3CNV7</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>AVat9lPF</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Wplk7SgS</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>2TvL16Hk</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>tzSnG5Wr</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>beYTapn2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>AiyHLR8L</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>jkLFNmv9</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>2kGeEq1e</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>UwFBuMaf</t>
+          <t>Of1jzRNE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GhtVSrGl</t>
+          <t>AFJ3CNV7</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -535,366 +535,6 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>OIqwRMp1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>pYXoP0FD</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>d8abY4hR</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>W2BSyvaJ</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Q58Kw0U6</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>dQG3srVs</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>xtzXn47K</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>C0axT3Xo</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Of1jzRNE</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>AFJ3CNV7</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>AVat9lPF</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Wplk7SgS</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>2TvL16Hk</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>tzSnG5Wr</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>beYTapn2</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>AiyHLR8L</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>jkLFNmv9</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>2kGeEq1e</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Of1jzRNE</t>
+          <t>KQ2pRs2b</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>AFJ3CNV7</t>
+          <t>SCsTyaGG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -535,6 +535,366 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>KnvLwLo4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>K0JghK0c</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>4hy7UG8j</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>bXkCusHi</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WQcQHwPp</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>GhdgPLWA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>l6f1Na1N</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>8MkyzwoT</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>UwFBuMaf</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>GhtVSrGl</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>OIqwRMp1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>W2BSyvaJ</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>d8abY4hR</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Q58Kw0U6</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>pYXoP0FD</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>xtzXn47K</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>dQG3srVs</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>C0axT3Xo</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>KQ2pRs2b</t>
+          <t>UwFBuMaf</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SCsTyaGG</t>
+          <t>GhtVSrGl</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -538,7 +538,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KnvLwLo4</t>
+          <t>OIqwRMp1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -558,7 +558,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>K0JghK0c</t>
+          <t>dQG3srVs</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -578,7 +578,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4hy7UG8j</t>
+          <t>Q58Kw0U6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -598,7 +598,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bXkCusHi</t>
+          <t>W2BSyvaJ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -618,7 +618,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WQcQHwPp</t>
+          <t>d8abY4hR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -638,7 +638,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>GhdgPLWA</t>
+          <t>pYXoP0FD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -658,7 +658,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>l6f1Na1N</t>
+          <t>xtzXn47K</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -678,7 +678,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>8MkyzwoT</t>
+          <t>C0axT3Xo</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -695,206 +695,6 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>UwFBuMaf</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>GhtVSrGl</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>OIqwRMp1</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>W2BSyvaJ</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>d8abY4hR</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>Q58Kw0U6</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>pYXoP0FD</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>xtzXn47K</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>dQG3srVs</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>C0axT3Xo</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,72 +436,94 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_home_against</t>
+          <t>mean_last_270_matches_mean_rat_player_start_home_against</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_int_rep_player_sub</t>
+          <t>mean_last_270_matches_mean_rat_player_start_away_against</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Of1jzRNE</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>fsjksfhd</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -514,14 +536,20 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>AFJ3CNV7</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>nywy5cp3</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -534,6 +562,478 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ltBAlx0M</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>l0Zi1FqS</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>tbEWgXy2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>YXAOeg7k</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>bFdtqGNq</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>SQM1jbV9</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>d6dJHzU8</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>r3Wq3yFF</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>KQ2pRs2b</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SCsTyaGG</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>KnvLwLo4</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>K0JghK0c</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>WQcQHwPp</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>l6f1Na1N</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>bXkCusHi</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>GhdgPLWA</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>4hy7UG8j</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>8MkyzwoT</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,12 +518,10 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>fsjksfhd</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
+          <t>SCsTyaGG</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -544,12 +542,10 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nywy5cp3</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
+          <t>KnvLwLo4</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -570,7 +566,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ltBAlx0M</t>
+          <t>K0JghK0c</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -589,19 +585,19 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0.1219067826425908</v>
+      </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>l0Zi1FqS</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
+          <t>l6f1Na1N</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -622,12 +618,10 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>tbEWgXy2</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
+          <t>WQcQHwPp</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -648,12 +642,10 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>YXAOeg7k</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
+          <t>bXkCusHi</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -674,7 +666,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bFdtqGNq</t>
+          <t>4hy7UG8j</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -687,25 +679,31 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>0.44917902892631</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.1583138611322483</v>
+      </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>-0.2889457398878397</v>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>0.1219067826425908</v>
+      </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SQM1jbV9</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
+          <t>GhdgPLWA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -726,12 +724,10 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>d6dJHzU8</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
+          <t>8MkyzwoT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -749,292 +745,6 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>r3Wq3yFF</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>KQ2pRs2b</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>SCsTyaGG</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>KnvLwLo4</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>K0JghK0c</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>WQcQHwPp</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>l6f1Na1N</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>bXkCusHi</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>GhdgPLWA</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>4hy7UG8j</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>8MkyzwoT</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SCsTyaGG</t>
+          <t>KQ2pRs2b</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -542,7 +542,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>KnvLwLo4</t>
+          <t>SCsTyaGG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -566,12 +566,10 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>K0JghK0c</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
+          <t>KnvLwLo4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -585,165 +583,9 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>0.1219067826425908</v>
-      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>l6f1Na1N</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>WQcQHwPp</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>bXkCusHi</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>4hy7UG8j</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="n">
-        <v>0.44917902892631</v>
-      </c>
-      <c r="K8" t="n">
-        <v>-0.1583138611322483</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="n">
-        <v>-0.2889457398878397</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="n">
-        <v>0.1219067826425908</v>
-      </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>GhdgPLWA</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>8MkyzwoT</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,92 +436,74 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_270_matches_mean_rat_player_start_home_against</t>
+          <t>dif_mean_value_player_start</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_270_matches_mean_rat_player_start_away_against</t>
+          <t>dif_mean_rep_player_start</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_wage_player_start</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_rat_player_miss</t>
+          <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
+          <t>dif_mean_pot_player_start</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>KQ2pRs2b</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>Gl6s8NdC</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -529,23 +511,23 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>0.00110585081648641</v>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SCsTyaGG</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>Y5lic6rf</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -553,23 +535,23 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>0.00110585081648641</v>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KnvLwLo4</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>tWiaepD6</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -577,15 +559,289 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>0.00110585081648641</v>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>UiYgHRZP</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>0.00110585081648641</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>n9EQB5cm</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>0.00110585081648641</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>OE9k61RO</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>0.00110585081648641</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>fsjksfhd</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ltBAlx0M</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>nywy5cp3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>l0Zi1FqS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>SQM1jbV9</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>bFdtqGNq</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>YXAOeg7k</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>tbEWgXy2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>d6dJHzU8</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>0.00110585081648641</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>r3Wq3yFF</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Gl6s8NdC</t>
+          <t>2ot8gOsJ</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -512,7 +512,7 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>0.00110585081648641</v>
+        <v>-0.2251193662171381</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -522,7 +522,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Y5lic6rf</t>
+          <t>SSZaQ4Ct</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -536,7 +536,7 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>0.00110585081648641</v>
+        <v>-0.2251193662171381</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -546,7 +546,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tWiaepD6</t>
+          <t>ShJjaSDs</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -560,7 +560,7 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>0.00110585081648641</v>
+        <v>-0.2251193662171381</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -570,7 +570,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>UiYgHRZP</t>
+          <t>n9EQB5cm</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -584,7 +584,7 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>0.00110585081648641</v>
+        <v>-0.2251193662171381</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -594,7 +594,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>n9EQB5cm</t>
+          <t>tWiaepD6</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -608,7 +608,7 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>0.00110585081648641</v>
+        <v>-0.2251193662171381</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -618,7 +618,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>OE9k61RO</t>
+          <t>Y5lic6rf</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -632,7 +632,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>0.00110585081648641</v>
+        <v>-0.2251193662171381</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -642,10 +642,12 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>fsjksfhd</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>UiYgHRZP</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -653,7 +655,9 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>-0.2251193662171381</v>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
@@ -662,10 +666,12 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ltBAlx0M</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>Gl6s8NdC</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -673,7 +679,9 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>-0.2251193662171381</v>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
@@ -682,10 +690,12 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>nywy5cp3</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>OE9k61RO</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -693,7 +703,9 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="n">
+        <v>-0.2251193662171381</v>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
@@ -702,7 +714,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>l0Zi1FqS</t>
+          <t>fsjksfhd</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -722,7 +734,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>SQM1jbV9</t>
+          <t>ltBAlx0M</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -742,7 +754,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bFdtqGNq</t>
+          <t>nywy5cp3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -759,90 +771,6 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>YXAOeg7k</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>tbEWgXy2</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>d6dJHzU8</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="n">
-        <v>0.00110585081648641</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>r3Wq3yFF</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2ot8gOsJ</t>
+          <t>EqY7Orsg</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -511,9 +511,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
-        <v>-0.2251193662171381</v>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -522,7 +520,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SSZaQ4Ct</t>
+          <t>EcDtwrdn</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -535,9 +533,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
-        <v>-0.2251193662171381</v>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -546,7 +542,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ShJjaSDs</t>
+          <t>EJlHkLuh</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -559,9 +555,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
-        <v>-0.2251193662171381</v>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -570,7 +564,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>n9EQB5cm</t>
+          <t>zD1kyMQb</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -583,9 +577,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
-        <v>-0.2251193662171381</v>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -594,7 +586,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>tWiaepD6</t>
+          <t>rw5cZaeB</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -607,9 +599,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="n">
-        <v>-0.2251193662171381</v>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -618,7 +608,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Y5lic6rf</t>
+          <t>zypxSHmo</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -631,9 +621,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>-0.2251193662171381</v>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -642,7 +630,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>UiYgHRZP</t>
+          <t>ABRGMMB5</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -655,9 +643,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="n">
-        <v>-0.2251193662171381</v>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
@@ -666,7 +652,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Gl6s8NdC</t>
+          <t>viJXIvBU</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -679,9 +665,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
-        <v>-0.2251193662171381</v>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
@@ -690,7 +674,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OE9k61RO</t>
+          <t>rPPOK0tI</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -703,9 +687,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="n">
-        <v>-0.2251193662171381</v>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
@@ -714,10 +696,12 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>fsjksfhd</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>v5b6XwQN</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
@@ -734,10 +718,12 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>ltBAlx0M</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>KMCY9qSa</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
@@ -754,10 +740,12 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>nywy5cp3</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t>2ot8gOsJ</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
@@ -771,6 +759,182 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>SSZaQ4Ct</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ShJjaSDs</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>UiYgHRZP</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>n9EQB5cm</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Y5lic6rf</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>tWiaepD6</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Gl6s8NdC</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>OE9k61RO</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,25 +471,20 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_hei_player_miss</t>
+          <t>dif_mean_wage_player_start</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_wage_player_start</t>
+          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_rat_player_sub</t>
+          <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_start</t>
         </is>
@@ -501,9 +496,7 @@
           <t>EqY7Orsg</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -515,7 +508,6 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -523,9 +515,7 @@
           <t>EcDtwrdn</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -537,7 +527,6 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -545,9 +534,7 @@
           <t>EJlHkLuh</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -559,7 +546,6 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -567,9 +553,7 @@
           <t>zD1kyMQb</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -581,7 +565,6 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -589,9 +572,7 @@
           <t>rw5cZaeB</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -603,7 +584,6 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -611,9 +591,7 @@
           <t>zypxSHmo</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -625,7 +603,6 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -633,9 +610,7 @@
           <t>ABRGMMB5</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -647,7 +622,6 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -655,9 +629,7 @@
           <t>viJXIvBU</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -669,7 +641,6 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -677,9 +648,7 @@
           <t>rPPOK0tI</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -691,7 +660,6 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -699,9 +667,7 @@
           <t>v5b6XwQN</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
@@ -713,7 +679,6 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -721,9 +686,7 @@
           <t>KMCY9qSa</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
@@ -735,7 +698,6 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -743,9 +705,7 @@
           <t>2ot8gOsJ</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
@@ -757,7 +717,6 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -765,9 +724,7 @@
           <t>SSZaQ4Ct</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
@@ -779,7 +736,6 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -787,9 +743,7 @@
           <t>ShJjaSDs</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
@@ -801,7 +755,6 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -809,9 +762,7 @@
           <t>UiYgHRZP</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
@@ -823,7 +774,6 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -831,9 +781,7 @@
           <t>n9EQB5cm</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
@@ -845,7 +793,6 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -853,9 +800,7 @@
           <t>Y5lic6rf</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
@@ -867,7 +812,6 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -875,9 +819,7 @@
           <t>tWiaepD6</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
@@ -889,7 +831,6 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -897,9 +838,7 @@
           <t>Gl6s8NdC</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
@@ -911,7 +850,6 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -919,9 +857,7 @@
           <t>OE9k61RO</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
@@ -933,7 +869,6 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>EqY7Orsg</t>
+          <t>KMCY9qSa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -512,7 +512,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EcDtwrdn</t>
+          <t>2ot8gOsJ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -531,7 +531,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EJlHkLuh</t>
+          <t>SSZaQ4Ct</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -547,329 +547,6 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>zD1kyMQb</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>rw5cZaeB</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>zypxSHmo</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>ABRGMMB5</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>viJXIvBU</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>rPPOK0tI</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>v5b6XwQN</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>KMCY9qSa</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>2ot8gOsJ</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>SSZaQ4Ct</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>ShJjaSDs</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>UiYgHRZP</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>n9EQB5cm</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Y5lic6rf</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>tWiaepD6</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Gl6s8NdC</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>OE9k61RO</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>KMCY9qSa</t>
+          <t>ratYowuH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -512,7 +512,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2ot8gOsJ</t>
+          <t>zil0kCo9</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -531,7 +531,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SSZaQ4Ct</t>
+          <t>drzevnw8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -547,6 +547,329 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>EJ4unbdE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>OGMmt88e</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>rc1ER8g2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>lb85TUOk</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>MqhPmaA4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>21YvrUwq</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>WIs9mjGL</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>EqY7Orsg</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>EJlHkLuh</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>zD1kyMQb</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>EcDtwrdn</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>rw5cZaeB</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ABRGMMB5</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>zypxSHmo</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>viJXIvBU</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>rPPOK0tI</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>v5b6XwQN</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ratYowuH</t>
+          <t>EqY7Orsg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -512,7 +512,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>zil0kCo9</t>
+          <t>EcDtwrdn</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -531,7 +531,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>drzevnw8</t>
+          <t>zD1kyMQb</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -550,7 +550,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EJ4unbdE</t>
+          <t>EJlHkLuh</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -569,7 +569,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>OGMmt88e</t>
+          <t>rw5cZaeB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -588,7 +588,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>rc1ER8g2</t>
+          <t>ABRGMMB5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -607,7 +607,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>lb85TUOk</t>
+          <t>rPPOK0tI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>MqhPmaA4</t>
+          <t>viJXIvBU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -645,7 +645,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>21YvrUwq</t>
+          <t>zypxSHmo</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -664,7 +664,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>WIs9mjGL</t>
+          <t>v5b6XwQN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -680,196 +680,6 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>EqY7Orsg</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>EJlHkLuh</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>zD1kyMQb</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>EcDtwrdn</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>rw5cZaeB</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ABRGMMB5</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>zypxSHmo</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>viJXIvBU</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>rPPOK0tI</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>v5b6XwQN</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>EqY7Orsg</t>
+          <t>CEnSxfJ0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -512,7 +512,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EcDtwrdn</t>
+          <t>hY71igYg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -531,7 +531,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>zD1kyMQb</t>
+          <t>KK9ggF3s</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -550,7 +550,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EJlHkLuh</t>
+          <t>CzO2kX26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -569,7 +569,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>rw5cZaeB</t>
+          <t>0zTMbytK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -588,7 +588,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ABRGMMB5</t>
+          <t>6HqKvGll</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -607,7 +607,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>rPPOK0tI</t>
+          <t>nX2mpxRQ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>viJXIvBU</t>
+          <t>YTzyyYmD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -645,7 +645,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zypxSHmo</t>
+          <t>K0RAmBXI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -664,7 +664,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>v5b6XwQN</t>
+          <t>0d4cBEPP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -680,6 +680,196 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ratYowuH</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>zil0kCo9</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>drzevnw8</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>EJ4unbdE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>OGMmt88e</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>21YvrUwq</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>MqhPmaA4</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>rc1ER8g2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>lb85TUOk</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>WIs9mjGL</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CEnSxfJ0</t>
+          <t>ratYowuH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -512,7 +512,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hY71igYg</t>
+          <t>zil0kCo9</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -531,7 +531,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KK9ggF3s</t>
+          <t>drzevnw8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -550,7 +550,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CzO2kX26</t>
+          <t>EJ4unbdE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -569,7 +569,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0zTMbytK</t>
+          <t>MqhPmaA4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -588,7 +588,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>6HqKvGll</t>
+          <t>lb85TUOk</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -607,7 +607,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nX2mpxRQ</t>
+          <t>rc1ER8g2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>YTzyyYmD</t>
+          <t>21YvrUwq</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -645,7 +645,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>K0RAmBXI</t>
+          <t>OGMmt88e</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -664,7 +664,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>0d4cBEPP</t>
+          <t>WIs9mjGL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -680,196 +680,6 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>ratYowuH</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>zil0kCo9</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>drzevnw8</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>EJ4unbdE</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>OGMmt88e</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>21YvrUwq</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>MqhPmaA4</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>rc1ER8g2</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>lb85TUOk</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>WIs9mjGL</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ratYowuH</t>
+          <t>CEnSxfJ0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -512,7 +512,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>zil0kCo9</t>
+          <t>KK9ggF3s</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -531,7 +531,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>drzevnw8</t>
+          <t>hY71igYg</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -550,7 +550,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EJ4unbdE</t>
+          <t>CzO2kX26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -569,7 +569,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>MqhPmaA4</t>
+          <t>0zTMbytK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -588,7 +588,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>lb85TUOk</t>
+          <t>6HqKvGll</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -607,7 +607,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>rc1ER8g2</t>
+          <t>nX2mpxRQ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>21YvrUwq</t>
+          <t>YTzyyYmD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -645,7 +645,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OGMmt88e</t>
+          <t>K0RAmBXI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -664,7 +664,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>WIs9mjGL</t>
+          <t>0d4cBEPP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>

--- a/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,64 +436,49 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_value_player_start</t>
+          <t>dif_mean_age_player_sub</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_rep_player_start</t>
+          <t>dif_mean_age_player_start</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_value_player_sub</t>
+          <t>dif_mean_hei_player_start</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_wage_player_sub</t>
+          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_age_player_start</t>
+          <t>dif_mean_rep_player_sub</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
           <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CEnSxfJ0</t>
+          <t>A7iT11hT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -505,14 +490,11 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>KK9ggF3s</t>
+          <t>Cl3y4WHa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -524,14 +506,11 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hY71igYg</t>
+          <t>v3JHq2Wp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -543,14 +522,11 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CzO2kX26</t>
+          <t>WveT5hmm</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -562,14 +538,11 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0zTMbytK</t>
+          <t>69B375Oi</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -581,14 +554,11 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>6HqKvGll</t>
+          <t>p21q2AnC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -600,14 +570,11 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nX2mpxRQ</t>
+          <t>EubK3NNG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -619,14 +586,11 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>YTzyyYmD</t>
+          <t>CEnSxfJ0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -638,14 +602,11 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>K0RAmBXI</t>
+          <t>KK9ggF3s</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -657,14 +618,11 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>0d4cBEPP</t>
+          <t>hY71igYg</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -676,9 +634,118 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CzO2kX26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>0zTMbytK</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>6HqKvGll</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>nX2mpxRQ</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>0d4cBEPP</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>K0RAmBXI</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>YTzyyYmD</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
